--- a/italy_values_dataset.xlsx
+++ b/italy_values_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oldan\Desktop\RuralDevelopment\progetto-tirocinio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4D4E64-124A-4AB9-92F5-1E4014AA82F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47442453-7DAD-4A06-BA4D-24F1C591942C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
